--- a/sch/airsens_p03/airsens_p03_implantation_v01.xlsx
+++ b/sch/airsens_p03/airsens_p03_implantation_v01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f34ccaa6039d8a87/technique/_projets/esp32-micropython/esp32-airsens/sch/airsens_p03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{0F2EF290-A8FF-4D81-8DB4-5882559B5281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5EF1119-2800-4A5A-8CA3-BB825A7EC24F}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{0F2EF290-A8FF-4D81-8DB4-5882559B5281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{921A112D-77C9-4A79-BBB6-D73410085B5A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="61">
   <si>
     <t>A</t>
   </si>
@@ -294,7 +294,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -691,6 +691,19 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -750,9 +763,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -768,6 +778,99 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -795,97 +898,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1187,41 +1200,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33"/>
-      <c r="B1" s="34">
+      <c r="A1" s="23"/>
+      <c r="B1" s="24">
         <v>1</v>
       </c>
-      <c r="C1" s="34">
+      <c r="C1" s="24">
         <v>2</v>
       </c>
-      <c r="D1" s="34">
+      <c r="D1" s="24">
         <v>3</v>
       </c>
-      <c r="E1" s="34">
+      <c r="E1" s="24">
         <v>4</v>
       </c>
-      <c r="F1" s="34">
+      <c r="F1" s="24">
         <v>5</v>
       </c>
-      <c r="G1" s="34">
+      <c r="G1" s="24">
         <v>6</v>
       </c>
-      <c r="H1" s="34">
+      <c r="H1" s="24">
         <v>7</v>
       </c>
-      <c r="I1" s="34">
+      <c r="I1" s="24">
         <v>8</v>
       </c>
-      <c r="J1" s="34">
+      <c r="J1" s="24">
         <v>9</v>
       </c>
-      <c r="K1" s="34">
+      <c r="K1" s="24">
         <v>10</v>
       </c>
-      <c r="L1" s="35"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2"/>
@@ -1229,21 +1242,21 @@
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="31" t="s">
         <v>24</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
-      <c r="J2" s="49" t="s">
+      <c r="J2" s="39" t="s">
         <v>25</v>
       </c>
       <c r="K2" s="3"/>
-      <c r="L2" s="37" t="s">
+      <c r="L2" s="27" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="26" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="4"/>
@@ -1260,12 +1273,12 @@
         <v>26</v>
       </c>
       <c r="K3" s="7"/>
-      <c r="L3" s="37" t="s">
+      <c r="L3" s="27" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="26" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="4"/>
@@ -1282,12 +1295,12 @@
         <v>32</v>
       </c>
       <c r="K4" s="7"/>
-      <c r="L4" s="37" t="s">
+      <c r="L4" s="27" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="26" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="4"/>
@@ -1295,23 +1308,23 @@
         <v>36</v>
       </c>
       <c r="D5" s="9"/>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="26"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="56"/>
       <c r="I5" s="9"/>
       <c r="J5" s="10" t="s">
         <v>33</v>
       </c>
       <c r="K5" s="7"/>
-      <c r="L5" s="37" t="s">
+      <c r="L5" s="27" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="26" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="4"/>
@@ -1319,21 +1332,21 @@
         <v>35</v>
       </c>
       <c r="D6" s="9"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="29"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="59"/>
       <c r="I6" s="9"/>
       <c r="J6" s="10" t="s">
         <v>27</v>
       </c>
       <c r="K6" s="7"/>
-      <c r="L6" s="37" t="s">
+      <c r="L6" s="27" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="26" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="4"/>
@@ -1341,41 +1354,41 @@
         <v>60</v>
       </c>
       <c r="D7" s="9"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="29"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="59"/>
       <c r="I7" s="9"/>
       <c r="J7" s="10" t="s">
         <v>28</v>
       </c>
       <c r="K7" s="7"/>
-      <c r="L7" s="37" t="s">
+      <c r="L7" s="27" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="26" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="8"/>
       <c r="D8" s="9"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="62"/>
       <c r="I8" s="9"/>
       <c r="J8" s="10" t="s">
         <v>29</v>
       </c>
       <c r="K8" s="7"/>
-      <c r="L8" s="37" t="s">
+      <c r="L8" s="27" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="26" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="4"/>
@@ -1392,12 +1405,12 @@
         <v>27</v>
       </c>
       <c r="K9" s="7"/>
-      <c r="L9" s="37" t="s">
+      <c r="L9" s="27" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="26" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="4"/>
@@ -1412,12 +1425,12 @@
         <v>30</v>
       </c>
       <c r="K10" s="7"/>
-      <c r="L10" s="37" t="s">
+      <c r="L10" s="27" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="26" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="4"/>
@@ -1436,12 +1449,12 @@
         <v>31</v>
       </c>
       <c r="K11" s="7"/>
-      <c r="L11" s="37" t="s">
+      <c r="L11" s="27" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="26" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="4"/>
@@ -1449,57 +1462,57 @@
       <c r="D12" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="48" t="s">
+      <c r="E12" s="38" t="s">
         <v>41</v>
       </c>
       <c r="F12" s="15"/>
-      <c r="G12" s="48" t="s">
+      <c r="G12" s="38" t="s">
         <v>44</v>
       </c>
       <c r="H12" s="15"/>
-      <c r="I12" s="48" t="s">
+      <c r="I12" s="38" t="s">
         <v>45</v>
       </c>
       <c r="J12" s="15"/>
-      <c r="K12" s="48" t="s">
+      <c r="K12" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="L12" s="37" t="s">
+      <c r="L12" s="27" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="48" t="s">
         <v>40</v>
       </c>
       <c r="C13" s="15"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
       <c r="F13" s="15"/>
-      <c r="G13" s="47"/>
+      <c r="G13" s="37"/>
       <c r="H13" s="15"/>
-      <c r="I13" s="47"/>
+      <c r="I13" s="37"/>
       <c r="J13" s="15"/>
-      <c r="K13" s="47"/>
-      <c r="L13" s="37" t="s">
+      <c r="K13" s="37"/>
+      <c r="L13" s="27" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="59" t="s">
+      <c r="B14" s="49" t="s">
         <v>53</v>
       </c>
       <c r="C14" s="15"/>
-      <c r="D14" s="42" t="s">
+      <c r="D14" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="48" t="s">
+      <c r="E14" s="38" t="s">
         <v>43</v>
       </c>
       <c r="F14" s="15"/>
@@ -1514,33 +1527,37 @@
       <c r="K14" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="L14" s="37" t="s">
+      <c r="L14" s="27" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="26" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="15"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="53"/>
+      <c r="D15" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>50</v>
+      </c>
       <c r="F15" s="15"/>
-      <c r="G15" s="43"/>
+      <c r="G15" s="33"/>
       <c r="H15" s="15"/>
-      <c r="I15" s="43"/>
+      <c r="I15" s="33"/>
       <c r="J15" s="15"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="37" t="s">
+      <c r="K15" s="33"/>
+      <c r="L15" s="27" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="60" t="s">
+      <c r="B16" s="50" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="15"/>
@@ -1552,74 +1569,74 @@
       <c r="I16" s="15"/>
       <c r="J16" s="15"/>
       <c r="K16" s="7"/>
-      <c r="L16" s="37" t="s">
+      <c r="L16" s="27" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="51" t="s">
         <v>54</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
-      <c r="E17" s="50" t="s">
+      <c r="E17" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="57" t="s">
+      <c r="F17" s="47" t="s">
         <v>55</v>
       </c>
       <c r="G17" s="15"/>
-      <c r="H17" s="62" t="s">
+      <c r="H17" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="I17" s="51"/>
+      <c r="I17" s="41"/>
       <c r="J17" s="15"/>
       <c r="K17" s="7"/>
-      <c r="L17" s="37" t="s">
+      <c r="L17" s="27" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="36" t="s">
+      <c r="A18" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="19" t="s">
         <v>31</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
-      <c r="E18" s="56" t="s">
+      <c r="E18" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="44"/>
+      <c r="F18" s="34"/>
       <c r="G18" s="15"/>
-      <c r="H18" s="19" t="s">
+      <c r="H18" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="I18" s="44"/>
+      <c r="I18" s="34"/>
       <c r="J18" s="15"/>
-      <c r="K18" s="20" t="s">
+      <c r="K18" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="L18" s="37" t="s">
+      <c r="L18" s="27" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="26" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="4"/>
-      <c r="C19" s="54" t="s">
+      <c r="C19" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="45" t="s">
+      <c r="D19" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="63" t="s">
+      <c r="E19" s="53" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="15"/>
@@ -1628,12 +1645,12 @@
       <c r="I19" s="15"/>
       <c r="J19" s="15"/>
       <c r="K19" s="7"/>
-      <c r="L19" s="37" t="s">
+      <c r="L19" s="27" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="36" t="s">
+      <c r="A20" s="26" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="4"/>
@@ -1646,44 +1663,44 @@
       <c r="I20" s="15"/>
       <c r="J20" s="15"/>
       <c r="K20" s="7"/>
-      <c r="L20" s="37" t="s">
+      <c r="L20" s="27" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="26" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="15"/>
-      <c r="D21" s="46" t="s">
+      <c r="D21" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="55" t="s">
+      <c r="E21" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F21" s="44" t="s">
+      <c r="F21" s="34" t="s">
         <v>24</v>
       </c>
       <c r="G21" s="15"/>
-      <c r="H21" s="19" t="s">
+      <c r="H21" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="I21" s="21" t="s">
+      <c r="I21" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="J21" s="52" t="s">
+      <c r="J21" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="44" t="s">
+      <c r="K21" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="L21" s="37" t="s">
+      <c r="L21" s="27" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="36" t="s">
+      <c r="A22" s="26" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="4"/>
@@ -1696,46 +1713,46 @@
       <c r="I22" s="15"/>
       <c r="J22" s="15"/>
       <c r="K22" s="7"/>
-      <c r="L22" s="37" t="s">
+      <c r="L22" s="27" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="36" t="s">
+      <c r="A23" s="26" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="15"/>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E23" s="21" t="s">
+      <c r="E23" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="21" t="s">
+      <c r="F23" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="21" t="s">
+      <c r="G23" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="H23" s="21" t="s">
+      <c r="H23" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="21" t="s">
+      <c r="I23" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="J23" s="52" t="s">
+      <c r="J23" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="K23" s="44" t="s">
+      <c r="K23" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="L23" s="37" t="s">
+      <c r="L23" s="27" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="36" t="s">
+      <c r="A24" s="26" t="s">
         <v>22</v>
       </c>
       <c r="B24" s="4"/>
@@ -1748,67 +1765,67 @@
       <c r="I24" s="15"/>
       <c r="J24" s="15"/>
       <c r="K24" s="7"/>
-      <c r="L24" s="37" t="s">
+      <c r="L24" s="27" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="21" t="s">
+      <c r="B25" s="21"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="H25" s="21" t="s">
+      <c r="H25" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
-      <c r="K25" s="44" t="s">
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="L25" s="37" t="s">
+      <c r="L25" s="27" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="38"/>
-      <c r="B26" s="39">
+      <c r="A26" s="28"/>
+      <c r="B26" s="29">
         <v>1</v>
       </c>
-      <c r="C26" s="39">
+      <c r="C26" s="29">
         <v>2</v>
       </c>
-      <c r="D26" s="39">
+      <c r="D26" s="29">
         <v>3</v>
       </c>
-      <c r="E26" s="39">
+      <c r="E26" s="29">
         <v>4</v>
       </c>
-      <c r="F26" s="39">
+      <c r="F26" s="29">
         <v>5</v>
       </c>
-      <c r="G26" s="39">
+      <c r="G26" s="29">
         <v>6</v>
       </c>
-      <c r="H26" s="39">
+      <c r="H26" s="29">
         <v>7</v>
       </c>
-      <c r="I26" s="39">
+      <c r="I26" s="29">
         <v>8</v>
       </c>
-      <c r="J26" s="39">
+      <c r="J26" s="29">
         <v>9</v>
       </c>
-      <c r="K26" s="39">
+      <c r="K26" s="29">
         <v>10</v>
       </c>
-      <c r="L26" s="40"/>
+      <c r="L26" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sch/airsens_p03/airsens_p03_implantation_v01.xlsx
+++ b/sch/airsens_p03/airsens_p03_implantation_v01.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f34ccaa6039d8a87/technique/_projets/esp32-micropython/esp32-airsens/sch/airsens_p03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="201" documentId="8_{0F2EF290-A8FF-4D81-8DB4-5882559B5281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E22D2394-184B-4B61-83BE-864BDD70501D}"/>
+  <xr:revisionPtr revIDLastSave="333" documentId="8_{0F2EF290-A8FF-4D81-8DB4-5882559B5281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24254176-B949-4C2D-91A2-035B745AA917}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="airsens implantation proto po3c" sheetId="2" r:id="rId1"/>
-    <sheet name="airsens implantation proto p03b" sheetId="1" r:id="rId2"/>
+    <sheet name="airsens proto dessous po3c-v1" sheetId="3" r:id="rId1"/>
+    <sheet name="airsens proto dessus po3c-v1" sheetId="4" r:id="rId2"/>
+    <sheet name="airsens proto po3c-v0" sheetId="2" r:id="rId3"/>
+    <sheet name="airsens implantation proto p03b" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="74">
   <si>
     <t>A</t>
   </si>
@@ -242,13 +245,19 @@
   </si>
   <si>
     <t>PPK-0</t>
+  </si>
+  <si>
+    <t>Vue coté soudures</t>
+  </si>
+  <si>
+    <t>Vue coté composants</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,8 +280,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,8 +347,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="39">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -717,6 +755,77 @@
     </border>
     <border>
       <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thick">
         <color indexed="64"/>
       </right>
@@ -726,11 +835,11 @@
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -738,70 +847,10 @@
     <border>
       <left/>
       <right/>
-      <top style="thick">
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -810,7 +859,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -974,38 +1023,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1016,28 +1035,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1049,7 +1062,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1060,6 +1073,115 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1069,6 +1191,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCFFFF"/>
       <color rgb="FFFF7C80"/>
       <color rgb="FFCC0000"/>
       <color rgb="FFFF5050"/>
@@ -1348,6 +1471,1214 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29EBF057-4CBD-45BC-A9DA-AC96F049415F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="12" width="11.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11"/>
+      <c r="B1" s="12">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12">
+        <v>2</v>
+      </c>
+      <c r="D1" s="12">
+        <v>3</v>
+      </c>
+      <c r="E1" s="12">
+        <v>4</v>
+      </c>
+      <c r="F1" s="12">
+        <v>5</v>
+      </c>
+      <c r="G1" s="12">
+        <v>6</v>
+      </c>
+      <c r="H1" s="12">
+        <v>7</v>
+      </c>
+      <c r="I1" s="12">
+        <v>8</v>
+      </c>
+      <c r="J1" s="12">
+        <v>9</v>
+      </c>
+      <c r="K1" s="12">
+        <v>10</v>
+      </c>
+      <c r="L1" s="13"/>
+    </row>
+    <row r="2" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="70">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="108" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="70">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="64" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="5"/>
+      <c r="L3" s="71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="70">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="5"/>
+      <c r="L4" s="71">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="70">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="71">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="70">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="73" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="5"/>
+      <c r="L6" s="71">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="70">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="78"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="71">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="70">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="78"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="71">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="70">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="71">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="70">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" s="5"/>
+      <c r="L10" s="71">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="70">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="71">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="70">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="56"/>
+      <c r="L12" s="71">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="70">
+        <v>12</v>
+      </c>
+      <c r="B13" s="65"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="71">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="70">
+        <v>13</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="J14" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="K14" s="56"/>
+      <c r="L14" s="71">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="70">
+        <v>14</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="60" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="55"/>
+      <c r="I15" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="56"/>
+      <c r="L15" s="71">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="70">
+        <v>15</v>
+      </c>
+      <c r="B16" s="65"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="67" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" s="55"/>
+      <c r="I16" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="J16" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="K16" s="56"/>
+      <c r="L16" s="71">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="70">
+        <v>16</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="55"/>
+      <c r="D17" s="85" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="55"/>
+      <c r="G17" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="55"/>
+      <c r="I17" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="56"/>
+      <c r="L17" s="71">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="70">
+        <v>17</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="82"/>
+      <c r="D18" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="83"/>
+      <c r="G18" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="55"/>
+      <c r="I18" s="55"/>
+      <c r="J18" s="82"/>
+      <c r="K18" s="56"/>
+      <c r="L18" s="71">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="35.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="70">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="82"/>
+      <c r="F19" s="55"/>
+      <c r="G19"/>
+      <c r="H19" s="82"/>
+      <c r="I19" s="82"/>
+      <c r="J19" s="82"/>
+      <c r="K19" s="56"/>
+      <c r="L19" s="71">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="70">
+        <v>19</v>
+      </c>
+      <c r="B20" s="66"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="55"/>
+      <c r="K20" s="86"/>
+      <c r="L20" s="71">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="70">
+        <v>20</v>
+      </c>
+      <c r="B21" s="66" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="I21" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="J21" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" s="86"/>
+      <c r="L21" s="71">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="70">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="55"/>
+      <c r="K22" s="86"/>
+      <c r="L22" s="71">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="70">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="84" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="33"/>
+      <c r="F23" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="86"/>
+      <c r="L23" s="71">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="70">
+        <v>23</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="59"/>
+      <c r="L24" s="71">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="16"/>
+      <c r="B25" s="17">
+        <v>1</v>
+      </c>
+      <c r="C25" s="17">
+        <v>2</v>
+      </c>
+      <c r="D25" s="17">
+        <v>3</v>
+      </c>
+      <c r="E25" s="17">
+        <v>4</v>
+      </c>
+      <c r="F25" s="17">
+        <v>5</v>
+      </c>
+      <c r="G25" s="17">
+        <v>6</v>
+      </c>
+      <c r="H25" s="17">
+        <v>7</v>
+      </c>
+      <c r="I25" s="17">
+        <v>8</v>
+      </c>
+      <c r="J25" s="17">
+        <v>9</v>
+      </c>
+      <c r="K25" s="17">
+        <v>10</v>
+      </c>
+      <c r="L25" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E6:H9"/>
+    <mergeCell ref="E2:H2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1" gridLines="1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="61" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"-,Gras"&amp;16&amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;Z&amp;F</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED493465-23BD-4DF5-BB77-62882B04DE99}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="12" width="11.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11"/>
+      <c r="B1" s="12">
+        <v>10</v>
+      </c>
+      <c r="C1" s="12">
+        <v>9</v>
+      </c>
+      <c r="D1" s="12">
+        <v>8</v>
+      </c>
+      <c r="E1" s="12">
+        <v>7</v>
+      </c>
+      <c r="F1" s="12">
+        <v>6</v>
+      </c>
+      <c r="G1" s="12">
+        <v>5</v>
+      </c>
+      <c r="H1" s="12">
+        <v>4</v>
+      </c>
+      <c r="I1" s="12">
+        <v>3</v>
+      </c>
+      <c r="J1" s="12">
+        <v>2</v>
+      </c>
+      <c r="K1" s="12">
+        <v>1</v>
+      </c>
+      <c r="L1" s="13"/>
+    </row>
+    <row r="2" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="70">
+        <v>1</v>
+      </c>
+      <c r="B2" s="91"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="107" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="35.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="70">
+        <v>2</v>
+      </c>
+      <c r="B3" s="92"/>
+      <c r="C3" s="88" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="70">
+        <v>3</v>
+      </c>
+      <c r="B4" s="92"/>
+      <c r="C4" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="97"/>
+      <c r="L4" s="71">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="70">
+        <v>4</v>
+      </c>
+      <c r="B5" s="92"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="97"/>
+      <c r="L5" s="71">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="70">
+        <v>5</v>
+      </c>
+      <c r="B6" s="92"/>
+      <c r="C6" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="73" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="97"/>
+      <c r="L6" s="71">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="70">
+        <v>6</v>
+      </c>
+      <c r="B7" s="92"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="78"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="97"/>
+      <c r="L7" s="71">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="70">
+        <v>7</v>
+      </c>
+      <c r="B8" s="92"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="78"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="97"/>
+      <c r="L8" s="71">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="70">
+        <v>8</v>
+      </c>
+      <c r="B9" s="92"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="97"/>
+      <c r="L9" s="71">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="70">
+        <v>9</v>
+      </c>
+      <c r="B10" s="92"/>
+      <c r="C10" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="97"/>
+      <c r="L10" s="71">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="70">
+        <v>10</v>
+      </c>
+      <c r="B11" s="92"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="97"/>
+      <c r="L11" s="71">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="70">
+        <v>11</v>
+      </c>
+      <c r="B12" s="92"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="97"/>
+      <c r="L12" s="71">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="70">
+        <v>12</v>
+      </c>
+      <c r="B13" s="93"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="100"/>
+      <c r="I13" s="100"/>
+      <c r="J13" s="99"/>
+      <c r="K13" s="98"/>
+      <c r="L13" s="71">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="70">
+        <v>13</v>
+      </c>
+      <c r="B14" s="92"/>
+      <c r="C14" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="72" t="s">
+        <v>48</v>
+      </c>
+      <c r="I14" s="99"/>
+      <c r="J14" s="99"/>
+      <c r="K14" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="L14" s="71">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="70">
+        <v>14</v>
+      </c>
+      <c r="B15" s="92"/>
+      <c r="C15" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="99"/>
+      <c r="F15" s="100" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="90" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" s="99"/>
+      <c r="J15" s="99"/>
+      <c r="K15" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="L15" s="71">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="70">
+        <v>15</v>
+      </c>
+      <c r="B16" s="92"/>
+      <c r="C16" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="99"/>
+      <c r="F16" s="67" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="100"/>
+      <c r="H16" s="100"/>
+      <c r="I16" s="99"/>
+      <c r="J16" s="99"/>
+      <c r="K16" s="98"/>
+      <c r="L16" s="71">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="70">
+        <v>16</v>
+      </c>
+      <c r="B17" s="92"/>
+      <c r="C17" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="99"/>
+      <c r="F17" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="99"/>
+      <c r="H17" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="I17" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="99"/>
+      <c r="K17" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="71">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="70">
+        <v>17</v>
+      </c>
+      <c r="B18" s="92"/>
+      <c r="C18" s="100"/>
+      <c r="D18" s="99"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="101"/>
+      <c r="H18" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="I18" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="100"/>
+      <c r="K18" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="71">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="35.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="70">
+        <v>18</v>
+      </c>
+      <c r="B19" s="92"/>
+      <c r="C19" s="100"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="99"/>
+      <c r="H19" s="100"/>
+      <c r="I19" s="100"/>
+      <c r="J19" s="100"/>
+      <c r="K19" s="97"/>
+      <c r="L19" s="71">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="70">
+        <v>19</v>
+      </c>
+      <c r="B20" s="93"/>
+      <c r="C20" s="99"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="100"/>
+      <c r="I20" s="100"/>
+      <c r="J20" s="100"/>
+      <c r="K20" s="103"/>
+      <c r="L20" s="71">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="70">
+        <v>20</v>
+      </c>
+      <c r="B21" s="93"/>
+      <c r="C21" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="72" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="104" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="J21" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" s="103" t="s">
+        <v>60</v>
+      </c>
+      <c r="L21" s="71">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="70">
+        <v>21</v>
+      </c>
+      <c r="B22" s="93"/>
+      <c r="C22" s="99"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="99"/>
+      <c r="F22" s="99"/>
+      <c r="G22" s="99"/>
+      <c r="H22" s="99"/>
+      <c r="I22" s="99"/>
+      <c r="J22" s="99"/>
+      <c r="K22" s="97"/>
+      <c r="L22" s="71">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="70">
+        <v>22</v>
+      </c>
+      <c r="B23" s="93"/>
+      <c r="C23" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="H23" s="72"/>
+      <c r="I23" s="104" t="s">
+        <v>62</v>
+      </c>
+      <c r="J23" s="99"/>
+      <c r="K23" s="97"/>
+      <c r="L23" s="71">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="70">
+        <v>23</v>
+      </c>
+      <c r="B24" s="94"/>
+      <c r="C24" s="105"/>
+      <c r="D24" s="105"/>
+      <c r="E24" s="105"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="105"/>
+      <c r="H24" s="105"/>
+      <c r="I24" s="105"/>
+      <c r="J24" s="105"/>
+      <c r="K24" s="106"/>
+      <c r="L24" s="71">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="16"/>
+      <c r="B25" s="17">
+        <v>10</v>
+      </c>
+      <c r="C25" s="17">
+        <v>9</v>
+      </c>
+      <c r="D25" s="17">
+        <v>8</v>
+      </c>
+      <c r="E25" s="17">
+        <v>7</v>
+      </c>
+      <c r="F25" s="17">
+        <v>6</v>
+      </c>
+      <c r="G25" s="17">
+        <v>5</v>
+      </c>
+      <c r="H25" s="17">
+        <v>4</v>
+      </c>
+      <c r="I25" s="17">
+        <v>3</v>
+      </c>
+      <c r="J25" s="17">
+        <v>2</v>
+      </c>
+      <c r="K25" s="17">
+        <v>1</v>
+      </c>
+      <c r="L25" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="E6:H9"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1" gridLines="1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="61" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"-,Gras"&amp;16&amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;Z&amp;F</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{848538CB-7AB2-41D2-8587-85C6824968EC}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -1393,47 +2724,49 @@
       <c r="L1" s="13"/>
     </row>
     <row r="2" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="82">
+      <c r="A2" s="70">
         <v>1</v>
       </c>
       <c r="B2" s="2"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="87" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="83">
+      <c r="L2" s="71">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="82">
+      <c r="A3" s="70">
         <v>2</v>
       </c>
       <c r="B3" s="4"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="75" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="76" t="s">
+      <c r="C3" s="61"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="64" t="s">
         <v>25</v>
       </c>
       <c r="K3" s="5"/>
-      <c r="L3" s="83">
+      <c r="L3" s="71">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="82">
+      <c r="A4" s="70">
         <v>3</v>
       </c>
       <c r="B4" s="4"/>
@@ -1450,12 +2783,12 @@
         <v>26</v>
       </c>
       <c r="K4" s="5"/>
-      <c r="L4" s="83">
+      <c r="L4" s="71">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="82">
+      <c r="A5" s="70">
         <v>4</v>
       </c>
       <c r="B5" s="4"/>
@@ -1468,16 +2801,14 @@
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
-      <c r="J5" s="49" t="s">
-        <v>31</v>
-      </c>
+      <c r="J5" s="49"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="83">
+      <c r="L5" s="71">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="82">
+      <c r="A6" s="70">
         <v>5</v>
       </c>
       <c r="B6" s="4"/>
@@ -1485,21 +2816,23 @@
         <v>35</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="E6" s="55" t="s">
+      <c r="E6" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="57"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="75"/>
       <c r="I6" s="6"/>
-      <c r="J6" s="49"/>
+      <c r="J6" s="49" t="s">
+        <v>31</v>
+      </c>
       <c r="K6" s="5"/>
-      <c r="L6" s="83">
+      <c r="L6" s="71">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="82">
+      <c r="A7" s="70">
         <v>6</v>
       </c>
       <c r="B7" s="4"/>
@@ -1507,81 +2840,79 @@
         <v>34</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="60"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="78"/>
       <c r="I7" s="6"/>
       <c r="J7" s="49"/>
       <c r="K7" s="5"/>
-      <c r="L7" s="83">
+      <c r="L7" s="71">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="82">
+      <c r="A8" s="70">
         <v>7</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="48"/>
       <c r="D8" s="6"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="60"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="78"/>
       <c r="I8" s="6"/>
       <c r="J8" s="49"/>
       <c r="K8" s="5"/>
-      <c r="L8" s="83">
+      <c r="L8" s="71">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="82">
+      <c r="A9" s="70">
         <v>8</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="48"/>
       <c r="D9" s="6"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="62"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="63"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="81"/>
       <c r="I9" s="6"/>
       <c r="J9" s="49"/>
       <c r="K9" s="5"/>
-      <c r="L9" s="83">
+      <c r="L9" s="71">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="82">
+      <c r="A10" s="70">
         <v>9</v>
       </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="48" t="s">
-        <v>64</v>
-      </c>
+      <c r="C10" s="48"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
-      <c r="J10" s="49"/>
+      <c r="J10" s="49" t="s">
+        <v>33</v>
+      </c>
       <c r="K10" s="5"/>
-      <c r="L10" s="83">
+      <c r="L10" s="71">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="82">
+      <c r="A11" s="70">
         <v>10</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="48" t="s">
-        <v>56</v>
-      </c>
+      <c r="C11" s="48"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -1590,229 +2921,225 @@
       <c r="I11" s="6"/>
       <c r="J11" s="49"/>
       <c r="K11" s="5"/>
-      <c r="L11" s="83">
+      <c r="L11" s="71">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="82">
+      <c r="A12" s="70">
         <v>11</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="50"/>
-      <c r="D12" s="51" t="s">
-        <v>57</v>
-      </c>
+      <c r="D12" s="51"/>
       <c r="E12" s="51"/>
       <c r="F12" s="51"/>
       <c r="G12" s="51"/>
       <c r="H12" s="51"/>
-      <c r="I12" s="51" t="s">
-        <v>33</v>
-      </c>
+      <c r="I12" s="51"/>
       <c r="J12" s="52"/>
-      <c r="K12" s="66"/>
-      <c r="L12" s="83">
+      <c r="K12" s="56"/>
+      <c r="L12" s="71">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="82">
+      <c r="A13" s="70">
         <v>12</v>
       </c>
-      <c r="B13" s="77"/>
+      <c r="B13" s="65"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="64"/>
-      <c r="K13" s="67"/>
-      <c r="L13" s="83">
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="71">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="82">
+      <c r="A14" s="70">
         <v>13</v>
       </c>
-      <c r="B14" s="77"/>
-      <c r="C14" s="26" t="s">
+      <c r="B14" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="J14" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="71"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="H14" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="64"/>
-      <c r="J14" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="K14" s="67"/>
-      <c r="L14" s="83">
+      <c r="K14" s="56"/>
+      <c r="L14" s="71">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="82">
+      <c r="A15" s="70">
         <v>14</v>
       </c>
-      <c r="B15" s="77"/>
-      <c r="C15" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="71"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="53" t="s">
+      <c r="B15" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="32" t="s">
+      <c r="F15" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="I15" s="64"/>
-      <c r="J15" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="K15" s="67"/>
-      <c r="L15" s="83">
+      <c r="G15" s="60" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="55"/>
+      <c r="I15" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="56"/>
+      <c r="L15" s="71">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="82">
+      <c r="A16" s="70">
         <v>15</v>
       </c>
-      <c r="B16" s="77"/>
-      <c r="C16" s="28" t="s">
+      <c r="B16" s="65"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="67" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" s="55"/>
+      <c r="I16" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="J16" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="64"/>
-      <c r="H16" s="64"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="70"/>
-      <c r="K16" s="67"/>
-      <c r="L16" s="83">
+      <c r="K16" s="56"/>
+      <c r="L16" s="71">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="82">
+      <c r="A17" s="70">
         <v>16</v>
       </c>
-      <c r="B17" s="77"/>
-      <c r="C17" s="29" t="s">
+      <c r="B17" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="55"/>
+      <c r="D17" s="85" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="55"/>
+      <c r="G17" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="55"/>
+      <c r="I17" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="J17" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="71"/>
-      <c r="F17" s="79" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17" s="7"/>
-      <c r="H17" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="I17" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="K17" s="67"/>
-      <c r="L17" s="83">
+      <c r="K17" s="56"/>
+      <c r="L17" s="71">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="82">
+      <c r="A18" s="70">
         <v>17</v>
       </c>
-      <c r="B18" s="72"/>
-      <c r="C18" s="71"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="71"/>
-      <c r="F18" s="80" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" s="7"/>
-      <c r="H18" s="35" t="s">
+      <c r="B18" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="82"/>
+      <c r="D18" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="I18" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="K18" s="67"/>
-      <c r="L18" s="83">
+      <c r="F18" s="83"/>
+      <c r="G18" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="55"/>
+      <c r="I18" s="55"/>
+      <c r="J18" s="82"/>
+      <c r="K18" s="56"/>
+      <c r="L18" s="71">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="82">
+    <row r="19" spans="1:12" ht="35.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="70">
         <v>18</v>
       </c>
       <c r="B19" s="4"/>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="83">
+      <c r="C19" s="82"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="82"/>
+      <c r="F19" s="55"/>
+      <c r="G19"/>
+      <c r="H19" s="82"/>
+      <c r="I19" s="82"/>
+      <c r="J19" s="82"/>
+      <c r="K19" s="56"/>
+      <c r="L19" s="71">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="82">
+    <row r="20" spans="1:12" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="70">
         <v>19</v>
       </c>
-      <c r="B20" s="78"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="67"/>
-      <c r="L20" s="83">
+      <c r="B20" s="66"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="55"/>
+      <c r="K20" s="86"/>
+      <c r="L20" s="71">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="82">
+      <c r="A21" s="70">
         <v>20</v>
       </c>
-      <c r="B21" s="78" t="s">
+      <c r="B21" s="66" t="s">
         <v>60</v>
       </c>
       <c r="C21" s="40" t="s">
@@ -1839,70 +3166,70 @@
       <c r="J21" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="K21" s="67"/>
-      <c r="L21" s="83">
+      <c r="K21" s="86"/>
+      <c r="L21" s="71">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="82">
+      <c r="A22" s="70">
         <v>21</v>
       </c>
       <c r="B22" s="4"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="70"/>
-      <c r="K22" s="67"/>
-      <c r="L22" s="83">
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="55"/>
+      <c r="K22" s="86"/>
+      <c r="L22" s="71">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="82">
+      <c r="A23" s="70">
         <v>22</v>
       </c>
       <c r="B23" s="4"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="65" t="s">
+      <c r="C23" s="55"/>
+      <c r="D23" s="84" t="s">
         <v>62</v>
       </c>
       <c r="E23" s="33"/>
       <c r="F23" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" s="42" t="s">
         <v>66</v>
-      </c>
-      <c r="G23" s="42" t="s">
-        <v>65</v>
       </c>
       <c r="H23" s="42"/>
       <c r="I23" s="42"/>
       <c r="J23" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="K23" s="67"/>
-      <c r="L23" s="83">
+      <c r="K23" s="86"/>
+      <c r="L23" s="71">
         <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="35.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="82">
+      <c r="A24" s="70">
         <v>23</v>
       </c>
       <c r="B24" s="9"/>
-      <c r="C24" s="68"/>
-      <c r="D24" s="68"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="68"/>
-      <c r="G24" s="68"/>
-      <c r="H24" s="68"/>
-      <c r="I24" s="68"/>
-      <c r="J24" s="68"/>
-      <c r="K24" s="69"/>
-      <c r="L24" s="83">
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="59"/>
+      <c r="L24" s="71">
         <v>23</v>
       </c>
     </row>
@@ -1954,7 +3281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2075,12 +3402,12 @@
         <v>35</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="55" t="s">
+      <c r="E5" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="57"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="75"/>
       <c r="I5" s="6"/>
       <c r="J5" s="49" t="s">
         <v>32</v>
@@ -2099,10 +3426,10 @@
         <v>34</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="60"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="78"/>
       <c r="I6" s="6"/>
       <c r="J6" s="49" t="s">
         <v>67</v>
@@ -2119,10 +3446,10 @@
       <c r="B7" s="4"/>
       <c r="C7" s="48"/>
       <c r="D7" s="6"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="60"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="78"/>
       <c r="I7" s="6"/>
       <c r="J7" s="49" t="s">
         <v>68</v>
@@ -2139,10 +3466,10 @@
       <c r="B8" s="4"/>
       <c r="C8" s="48"/>
       <c r="D8" s="6"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="63"/>
+      <c r="E8" s="79"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="81"/>
       <c r="I8" s="6"/>
       <c r="J8" s="49" t="s">
         <v>69</v>
